--- a/001_Can_SapCoupa_CIBC_Dispatcher/Data/GMCAN_RPA001_Dispatcher_Config.xlsx
+++ b/001_Can_SapCoupa_CIBC_Dispatcher/Data/GMCAN_RPA001_Dispatcher_Config.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\grmusarpadev09\OneDrive - insidemedia.net\Desktop\Linktera\Aniket\New_001_Can_SapCoupa_CIBC\001_Can_SapCoupa_CIBC\001_Can_SapCoupa_CIBC_Dispatcher\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\1files\uipath\projects\001_Can_SapCoupa_CIBC\001_Can_SapCoupa_CIBC_Dispatcher\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C1C33DC-7B5C-4676-8469-243D07D160A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{054687FE-1073-416A-A3AC-8D0501F14F66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20700" windowHeight="8745" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="73">
   <si>
     <t>Name</t>
   </si>
@@ -257,16 +257,13 @@
   </si>
   <si>
     <t>aniketni@cybage.com</t>
-  </si>
-  <si>
-    <t>GMCAN_FINANCE_AR</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -296,6 +293,12 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -314,10 +317,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -328,8 +332,10 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -762,7 +768,7 @@
       <c r="A13" t="s">
         <v>63</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="6" t="s">
         <v>72</v>
       </c>
       <c r="C13" t="s">
@@ -3007,9 +3013,6 @@
       <c r="B2" t="s">
         <v>43</v>
       </c>
-      <c r="C2" t="s">
-        <v>73</v>
-      </c>
       <c r="D2" t="s">
         <v>45</v>
       </c>
@@ -3021,9 +3024,6 @@
       <c r="B3" t="s">
         <v>48</v>
       </c>
-      <c r="C3" t="s">
-        <v>73</v>
-      </c>
       <c r="D3" t="s">
         <v>49</v>
       </c>
@@ -3034,9 +3034,6 @@
       </c>
       <c r="B4" t="s">
         <v>69</v>
-      </c>
-      <c r="C4" t="s">
-        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1"/>
@@ -4042,27 +4039,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="7f25b792-b2ba-4b5c-8669-b39a27555406" xsi:nil="true"/>
-    <Time xmlns="649a79cd-06e4-47a3-aac9-21cb806f3675" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="649a79cd-06e4-47a3-aac9-21cb806f3675">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010045A9A53AB2AD7C409EFC96CC55961B83" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="9ff56ad652d5e5faec097a6229aaa81f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="649a79cd-06e4-47a3-aac9-21cb806f3675" xmlns:ns3="7f25b792-b2ba-4b5c-8669-b39a27555406" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3487cd39016dc6f53b8dc1d1dd8e1aa7" ns2:_="" ns3:_="">
     <xsd:import namespace="649a79cd-06e4-47a3-aac9-21cb806f3675"/>
@@ -4297,40 +4273,35 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="7f25b792-b2ba-4b5c-8669-b39a27555406" xsi:nil="true"/>
+    <Time xmlns="649a79cd-06e4-47a3-aac9-21cb806f3675" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="649a79cd-06e4-47a3-aac9-21cb806f3675">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBC5319C-25FF-4D19-A891-9E1D41D51C5F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA3898FF-5243-4254-8C81-1DAA66AD337D}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC6D4D96-92AB-4FE6-B8A3-A658E611DA49}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="7f25b792-b2ba-4b5c-8669-b39a27555406"/>
-    <ds:schemaRef ds:uri="649a79cd-06e4-47a3-aac9-21cb806f3675"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBC5319C-25FF-4D19-A891-9E1D41D51C5F}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA3898FF-5243-4254-8C81-1DAA66AD337D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="649a79cd-06e4-47a3-aac9-21cb806f3675"/>
-    <ds:schemaRef ds:uri="7f25b792-b2ba-4b5c-8669-b39a27555406"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC6D4D96-92AB-4FE6-B8A3-A658E611DA49}"/>
 </file>
--- a/001_Can_SapCoupa_CIBC_Dispatcher/Data/GMCAN_RPA001_Dispatcher_Config.xlsx
+++ b/001_Can_SapCoupa_CIBC_Dispatcher/Data/GMCAN_RPA001_Dispatcher_Config.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27425"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\1files\uipath\projects\001_Can_SapCoupa_CIBC\001_Can_SapCoupa_CIBC_Dispatcher\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\grmusarpadev09\OneDrive - insidemedia.net\Desktop\Linktera\Aniket\New_001_Can_SapCoupa_CIBC\001_Can_SapCoupa_CIBC\001_Can_SapCoupa_CIBC_Dispatcher\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{054687FE-1073-416A-A3AC-8D0501F14F66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{139017A9-B5AE-4466-934A-5E73939A324D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="13425" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="73">
   <si>
     <t>Name</t>
   </si>
@@ -208,9 +208,6 @@
     <t>RPA001_CIBC_Coupa_Dispatcher_Queue</t>
   </si>
   <si>
-    <t>bulent.yarbasi@linktera.com</t>
-  </si>
-  <si>
     <t>CIBC</t>
   </si>
   <si>
@@ -257,13 +254,16 @@
   </si>
   <si>
     <t>aniketni@cybage.com</t>
+  </si>
+  <si>
+    <t>GMCAN_FINANCE_AR</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -293,12 +293,6 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -317,11 +311,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -332,10 +325,8 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -352,9 +343,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -392,7 +383,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -498,7 +489,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -640,7 +631,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -704,10 +695,10 @@
     </row>
     <row r="3" spans="1:26" ht="14.25" customHeight="1">
       <c r="A3" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>60</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>21</v>
@@ -752,7 +743,7 @@
         <v>51</v>
       </c>
       <c r="B10" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1">
@@ -766,54 +757,51 @@
     <row r="12" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="13" spans="1:26" ht="14.25" customHeight="1">
       <c r="A13" t="s">
-        <v>63</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C13" t="s">
-        <v>56</v>
+        <v>62</v>
+      </c>
+      <c r="B13" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="15" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="16" spans="1:26" ht="14.25" customHeight="1">
       <c r="A16" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B16" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:2" ht="14.25" customHeight="1">
       <c r="A17" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="19" spans="1:2" ht="14.25" customHeight="1"/>
     <row r="20" spans="1:2" ht="14.25" customHeight="1">
       <c r="A20" s="5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:2" ht="14.25" customHeight="1">
       <c r="A21" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="1:2" ht="14.25" customHeight="1">
       <c r="A22" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>66</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:2" ht="14.25" customHeight="1"/>
@@ -1874,7 +1862,7 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C5" t="s">
         <v>7</v>
@@ -3013,6 +3001,9 @@
       <c r="B2" t="s">
         <v>43</v>
       </c>
+      <c r="C2" t="s">
+        <v>72</v>
+      </c>
       <c r="D2" t="s">
         <v>45</v>
       </c>
@@ -3024,16 +3015,22 @@
       <c r="B3" t="s">
         <v>48</v>
       </c>
+      <c r="C3" t="s">
+        <v>72</v>
+      </c>
       <c r="D3" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="14.25" customHeight="1">
       <c r="A4" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" t="s">
         <v>68</v>
       </c>
-      <c r="B4" t="s">
-        <v>69</v>
+      <c r="C4" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="14.25" customHeight="1"/>
@@ -4274,15 +4271,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="7f25b792-b2ba-4b5c-8669-b39a27555406" xsi:nil="true"/>
@@ -4294,14 +4282,49 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA3898FF-5243-4254-8C81-1DAA66AD337D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AA3898FF-5243-4254-8C81-1DAA66AD337D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="649a79cd-06e4-47a3-aac9-21cb806f3675"/>
+    <ds:schemaRef ds:uri="7f25b792-b2ba-4b5c-8669-b39a27555406"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBC5319C-25FF-4D19-A891-9E1D41D51C5F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC6D4D96-92AB-4FE6-B8A3-A658E611DA49}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="7f25b792-b2ba-4b5c-8669-b39a27555406"/>
+    <ds:schemaRef ds:uri="649a79cd-06e4-47a3-aac9-21cb806f3675"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC6D4D96-92AB-4FE6-B8A3-A658E611DA49}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DBC5319C-25FF-4D19-A891-9E1D41D51C5F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>